--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:36</t>
+    <t xml:space="preserve">2026-09-09 21:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:35</t>
+    <t xml:space="preserve">2026-09-16 21:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 21:14</t>
+    <t xml:space="preserve">2026-09-29 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -439,7 +439,7 @@
         <v>2019</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5.86</v>
+        <v>58.63</v>
       </c>
     </row>
     <row r="3">
@@ -447,7 +447,7 @@
         <v>2020</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7.3</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         <v>2021</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9.1</v>
+        <v>90.95</v>
       </c>
     </row>
     <row r="5">
@@ -463,7 +463,7 @@
         <v>2022</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>8.69</v>
+        <v>86.91</v>
       </c>
     </row>
     <row r="6">
@@ -471,7 +471,7 @@
         <v>2023</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>8.61</v>
+        <v>86.11</v>
       </c>
     </row>
     <row r="7">
@@ -479,7 +479,7 @@
         <v>2024</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>9.09</v>
+        <v>90.89</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:04</t>
+    <t xml:space="preserve">2026-10-01 19:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Tasa global de movilidad interna (CMI)</t>
+    <t xml:space="preserve">Tasa global de movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_m_movinterna_a_2019.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:29</t>
+    <t xml:space="preserve">2026-10-05 19:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
